--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Innovation Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Innovation Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="207">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Innovation Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -73,6 +73,15 @@
     <t>Banks</t>
   </si>
   <si>
+    <t>Reliance Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE002A01018</t>
+  </si>
+  <si>
+    <t>Petroleum Products</t>
+  </si>
+  <si>
     <t>Pidilite Industries Ltd.</t>
   </si>
   <si>
@@ -82,6 +91,30 @@
     <t>Chemicals &amp; Petrochemicals</t>
   </si>
   <si>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
+  </si>
+  <si>
+    <t>Maruti Suzuki India Ltd.</t>
+  </si>
+  <si>
+    <t>INE585B01010</t>
+  </si>
+  <si>
+    <t>Automobiles</t>
+  </si>
+  <si>
+    <t>Bharti Airtel Ltd.</t>
+  </si>
+  <si>
+    <t>INE397D01024</t>
+  </si>
+  <si>
+    <t>Telecom - Services</t>
+  </si>
+  <si>
     <t>Lupin Ltd.</t>
   </si>
   <si>
@@ -91,22 +124,34 @@
     <t>Pharmaceuticals &amp; Biotechnology</t>
   </si>
   <si>
-    <t>Reliance Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE002A01018</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
-  </si>
-  <si>
-    <t>Maruti Suzuki India Ltd.</t>
-  </si>
-  <si>
-    <t>INE585B01010</t>
-  </si>
-  <si>
-    <t>Automobiles</t>
+    <t>Mahindra &amp; Mahindra Ltd.</t>
+  </si>
+  <si>
+    <t>INE101A01026</t>
+  </si>
+  <si>
+    <t>Bharti Airtel Ltd. - Partly Paid Share</t>
+  </si>
+  <si>
+    <t>IN9397D01014</t>
+  </si>
+  <si>
+    <t>Infosys Ltd.</t>
+  </si>
+  <si>
+    <t>INE009A01021</t>
+  </si>
+  <si>
+    <t>It - Software</t>
+  </si>
+  <si>
+    <t>Larsen &amp; Toubro Ltd.</t>
+  </si>
+  <si>
+    <t>INE018A01030</t>
+  </si>
+  <si>
+    <t>Construction</t>
   </si>
   <si>
     <t>Sun Pharmaceutical Industries Ltd.</t>
@@ -115,6 +160,279 @@
     <t>INE044A01036</t>
   </si>
   <si>
+    <t>TVS Motor Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE494B01023</t>
+  </si>
+  <si>
+    <t>Godrej Consumer Products Ltd.</t>
+  </si>
+  <si>
+    <t>INE102D01028</t>
+  </si>
+  <si>
+    <t>Personal Products</t>
+  </si>
+  <si>
+    <t>Power Grid Corporation Of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE752E01010</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>LTIMindtree Ltd.</t>
+  </si>
+  <si>
+    <t>INE214T01019</t>
+  </si>
+  <si>
+    <t>Hyundai Motor India Ltd.</t>
+  </si>
+  <si>
+    <t>INE0V6F01027</t>
+  </si>
+  <si>
+    <t>Hindustan Unilever Ltd.</t>
+  </si>
+  <si>
+    <t>INE030A01027</t>
+  </si>
+  <si>
+    <t>Diversified Fmcg</t>
+  </si>
+  <si>
+    <t>Aurobindo Pharma Ltd.</t>
+  </si>
+  <si>
+    <t>INE406A01037</t>
+  </si>
+  <si>
+    <t>Info Edge (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE663F01032</t>
+  </si>
+  <si>
+    <t>Retailing</t>
+  </si>
+  <si>
+    <t>Syngene International Ltd.</t>
+  </si>
+  <si>
+    <t>INE398R01022</t>
+  </si>
+  <si>
+    <t>Healthcare Services</t>
+  </si>
+  <si>
+    <t>NTPC Ltd.</t>
+  </si>
+  <si>
+    <t>INE733E01010</t>
+  </si>
+  <si>
+    <t>HDFC Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE795G01014</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>Avenue Supermarts Ltd.</t>
+  </si>
+  <si>
+    <t>INE192R01011</t>
+  </si>
+  <si>
+    <t>Trent Ltd.</t>
+  </si>
+  <si>
+    <t>INE849A01020</t>
+  </si>
+  <si>
+    <t>ABB India Ltd.</t>
+  </si>
+  <si>
+    <t>INE117A01022</t>
+  </si>
+  <si>
+    <t>Electrical Equipment</t>
+  </si>
+  <si>
+    <t>Zydus Lifesciences Ltd.</t>
+  </si>
+  <si>
+    <t>INE010B01027</t>
+  </si>
+  <si>
+    <t>KEI Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE878B01027</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
+  </si>
+  <si>
+    <t>HDFC Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE040A01034</t>
+  </si>
+  <si>
+    <t>Sagility India Ltd</t>
+  </si>
+  <si>
+    <t>INE0W2G01015</t>
+  </si>
+  <si>
+    <t>It - Services</t>
+  </si>
+  <si>
+    <t>Cummins India Ltd.</t>
+  </si>
+  <si>
+    <t>INE298A01020</t>
+  </si>
+  <si>
+    <t>Oil India Ltd.</t>
+  </si>
+  <si>
+    <t>INE274J01014</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>Zomato Ltd.</t>
+  </si>
+  <si>
+    <t>INE758T01015</t>
+  </si>
+  <si>
+    <t>360 One Wam Ltd.</t>
+  </si>
+  <si>
+    <t>INE466L01038</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>Aditya Birla Sun Life AMC Ltd.</t>
+  </si>
+  <si>
+    <t>INE404A01024</t>
+  </si>
+  <si>
+    <t>Vinati Organics Ltd.</t>
+  </si>
+  <si>
+    <t>INE410B01037</t>
+  </si>
+  <si>
+    <t>Siemens Ltd.</t>
+  </si>
+  <si>
+    <t>INE003A01024</t>
+  </si>
+  <si>
+    <t>Supreme Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE195A01028</t>
+  </si>
+  <si>
+    <t>Dabur India Ltd.</t>
+  </si>
+  <si>
+    <t>INE016A01026</t>
+  </si>
+  <si>
+    <t>SIEMENS ENERGY INDIA LTD</t>
+  </si>
+  <si>
+    <t>INE1NPP01017</t>
+  </si>
+  <si>
+    <t>Birlasoft Ltd.</t>
+  </si>
+  <si>
+    <t>INE836A01035</t>
+  </si>
+  <si>
+    <t>Samvardhana Motherson International Ltd.</t>
+  </si>
+  <si>
+    <t>INE775A01035</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
+  </si>
+  <si>
+    <t>Motherson Sumi Wiring India Ltd.</t>
+  </si>
+  <si>
+    <t>INE0FS801015</t>
+  </si>
+  <si>
+    <t>KSB Ltd.</t>
+  </si>
+  <si>
+    <t>INE999A01023</t>
+  </si>
+  <si>
+    <t>Star Health &amp; Allied Insurance</t>
+  </si>
+  <si>
+    <t>INE575P01011</t>
+  </si>
+  <si>
+    <t>Acme Solar Holdings Ltd</t>
+  </si>
+  <si>
+    <t>INE622W01025</t>
+  </si>
+  <si>
+    <t>Kalpataru Projects International Ltd</t>
+  </si>
+  <si>
+    <t>INE220B01022</t>
+  </si>
+  <si>
+    <t>Computer Age Management Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE596I01012</t>
+  </si>
+  <si>
+    <t>AIA Engineering Ltd.</t>
+  </si>
+  <si>
+    <t>INE212H01026</t>
+  </si>
+  <si>
+    <t>ITC Ltd.</t>
+  </si>
+  <si>
+    <t>INE154A01025</t>
+  </si>
+  <si>
+    <t>Brigade Enterprises Ltd.</t>
+  </si>
+  <si>
+    <t>INE791I01019</t>
+  </si>
+  <si>
+    <t>Realty</t>
+  </si>
+  <si>
     <t>Havells India Ltd.</t>
   </si>
   <si>
@@ -124,346 +442,13 @@
     <t>Consumer Durables</t>
   </si>
   <si>
-    <t>Mahindra &amp; Mahindra Ltd.</t>
-  </si>
-  <si>
-    <t>INE101A01026</t>
-  </si>
-  <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
-  </si>
-  <si>
-    <t>LTIMindtree Ltd.</t>
-  </si>
-  <si>
-    <t>INE214T01019</t>
-  </si>
-  <si>
-    <t>It - Software</t>
-  </si>
-  <si>
-    <t>Bharti Airtel Ltd.</t>
-  </si>
-  <si>
-    <t>INE397D01024</t>
-  </si>
-  <si>
-    <t>Telecom - Services</t>
-  </si>
-  <si>
-    <t>Bharti Airtel Ltd. - Partly Paid Share</t>
-  </si>
-  <si>
-    <t>IN9397D01014</t>
-  </si>
-  <si>
-    <t>TVS Motor Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE494B01023</t>
-  </si>
-  <si>
-    <t>Larsen &amp; Toubro Ltd.</t>
-  </si>
-  <si>
-    <t>INE018A01030</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>Infosys Ltd.</t>
-  </si>
-  <si>
-    <t>INE009A01021</t>
-  </si>
-  <si>
-    <t>Godrej Consumer Products Ltd.</t>
-  </si>
-  <si>
-    <t>INE102D01028</t>
-  </si>
-  <si>
-    <t>Personal Products</t>
-  </si>
-  <si>
-    <t>HDFC Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE795G01014</t>
-  </si>
-  <si>
-    <t>Insurance</t>
-  </si>
-  <si>
-    <t>HDFC Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE040A01034</t>
-  </si>
-  <si>
-    <t>Hindustan Unilever Ltd.</t>
-  </si>
-  <si>
-    <t>INE030A01027</t>
-  </si>
-  <si>
-    <t>Diversified Fmcg</t>
-  </si>
-  <si>
-    <t>Cummins India Ltd.</t>
-  </si>
-  <si>
-    <t>INE298A01020</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
-  </si>
-  <si>
-    <t>Power Grid Corporation Of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE752E01010</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>Siemens Ltd.</t>
-  </si>
-  <si>
-    <t>INE003A01024</t>
-  </si>
-  <si>
-    <t>Electrical Equipment</t>
-  </si>
-  <si>
-    <t>Info Edge (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE663F01024</t>
-  </si>
-  <si>
-    <t>Retailing</t>
-  </si>
-  <si>
-    <t>Avenue Supermarts Ltd.</t>
-  </si>
-  <si>
-    <t>INE192R01011</t>
-  </si>
-  <si>
-    <t>Syngene International Ltd.</t>
-  </si>
-  <si>
-    <t>INE398R01022</t>
-  </si>
-  <si>
-    <t>Healthcare Services</t>
-  </si>
-  <si>
-    <t>Zydus Lifesciences Ltd.</t>
-  </si>
-  <si>
-    <t>INE010B01027</t>
-  </si>
-  <si>
-    <t>NTPC Ltd.</t>
-  </si>
-  <si>
-    <t>INE733E01010</t>
-  </si>
-  <si>
-    <t>ABB India Ltd.</t>
-  </si>
-  <si>
-    <t>INE117A01022</t>
-  </si>
-  <si>
-    <t>Trent Ltd.</t>
-  </si>
-  <si>
-    <t>INE849A01020</t>
-  </si>
-  <si>
-    <t>Nestle India Ltd.</t>
-  </si>
-  <si>
-    <t>INE239A01024</t>
-  </si>
-  <si>
-    <t>Food Products</t>
-  </si>
-  <si>
-    <t>Aurobindo Pharma Ltd.</t>
-  </si>
-  <si>
-    <t>INE406A01037</t>
-  </si>
-  <si>
-    <t>SRF Ltd.</t>
-  </si>
-  <si>
-    <t>INE647A01010</t>
-  </si>
-  <si>
-    <t>Supreme Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE195A01028</t>
-  </si>
-  <si>
-    <t>Vinati Organics Ltd.</t>
-  </si>
-  <si>
-    <t>INE410B01037</t>
-  </si>
-  <si>
-    <t>Astrazeneca Pharma India Ltd.</t>
-  </si>
-  <si>
-    <t>INE203A01020</t>
-  </si>
-  <si>
-    <t>Hindalco Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE038A01020</t>
-  </si>
-  <si>
-    <t>Non - Ferrous Metals</t>
-  </si>
-  <si>
-    <t>Max Financial Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE180A01020</t>
-  </si>
-  <si>
-    <t>Sagility India Ltd</t>
-  </si>
-  <si>
-    <t>INE0W2G01015</t>
-  </si>
-  <si>
-    <t>It - Services</t>
-  </si>
-  <si>
-    <t>KEI Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE878B01027</t>
-  </si>
-  <si>
-    <t>Dabur India Ltd.</t>
-  </si>
-  <si>
-    <t>INE016A01026</t>
-  </si>
-  <si>
-    <t>Eicher Motors Ltd.</t>
-  </si>
-  <si>
-    <t>INE066A01021</t>
-  </si>
-  <si>
-    <t>Acme Solar Holdings Ltd</t>
-  </si>
-  <si>
-    <t>INE622W01025</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>Navin Fluorine International Ltd.</t>
-  </si>
-  <si>
-    <t>INE048G01026</t>
-  </si>
-  <si>
-    <t>Divi's Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE361B01024</t>
-  </si>
-  <si>
-    <t>Bata India Ltd.</t>
-  </si>
-  <si>
-    <t>INE176A01028</t>
-  </si>
-  <si>
-    <t>Vishal Mega Mart Ltd.</t>
-  </si>
-  <si>
-    <t>INE01EA01019</t>
-  </si>
-  <si>
-    <t>Samvardhana Motherson International Ltd.</t>
-  </si>
-  <si>
-    <t>INE775A01035</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>Hitachi Energy India Ltd.</t>
-  </si>
-  <si>
-    <t>INE07Y701011</t>
-  </si>
-  <si>
-    <t>Star Health &amp; Allied Insurance</t>
-  </si>
-  <si>
-    <t>INE575P01011</t>
-  </si>
-  <si>
-    <t>Kalpataru Projects International Ltd</t>
-  </si>
-  <si>
-    <t>INE220B01022</t>
-  </si>
-  <si>
-    <t>Ge Vernova T&amp;D India Ltd.</t>
-  </si>
-  <si>
-    <t>INE200A01026</t>
-  </si>
-  <si>
-    <t>KSB Ltd.</t>
-  </si>
-  <si>
-    <t>INE999A01023</t>
-  </si>
-  <si>
-    <t>NHPC Ltd.</t>
-  </si>
-  <si>
-    <t>INE848E01016</t>
-  </si>
-  <si>
-    <t>Hindustan Aeronautics Ltd.</t>
-  </si>
-  <si>
-    <t>INE066F01020</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense</t>
-  </si>
-  <si>
-    <t>International Gemmological Institute (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE0Q9301021</t>
-  </si>
-  <si>
-    <t>Commercial Services &amp; Supplies</t>
+    <t>Yatra Online Ltd</t>
+  </si>
+  <si>
+    <t>INE0JR601024</t>
+  </si>
+  <si>
+    <t>Leisure Services</t>
   </si>
   <si>
     <t>Concord Enviro Systems Ltd</t>
@@ -475,72 +460,15 @@
     <t>Other Utilities</t>
   </si>
   <si>
-    <t>Bajaj Electricals Ltd.</t>
-  </si>
-  <si>
-    <t>INE193E01025</t>
-  </si>
-  <si>
-    <t>Netweb Technologies India</t>
-  </si>
-  <si>
-    <t>INE0NT901020</t>
-  </si>
-  <si>
-    <t>PI Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE603J01030</t>
-  </si>
-  <si>
-    <t>Fertilizers &amp; Agrochemicals</t>
-  </si>
-  <si>
-    <t>Yatra Online Ltd</t>
-  </si>
-  <si>
-    <t>INE0JR601024</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
-    <t>PSP Projects Ltd</t>
-  </si>
-  <si>
-    <t>INE488V01015</t>
-  </si>
-  <si>
-    <t>CYIENT DLM LTD</t>
-  </si>
-  <si>
-    <t>INE055S01018</t>
-  </si>
-  <si>
-    <t>Industrial Manufacturing</t>
+    <t>Life Insurance Corporation of India</t>
+  </si>
+  <si>
+    <t>INE0J1Y01017</t>
   </si>
   <si>
     <t>Foreign Securities/Overseas ETFs</t>
   </si>
   <si>
-    <t>Oracle Corp</t>
-  </si>
-  <si>
-    <t>US68389X1054</t>
-  </si>
-  <si>
-    <t>Software</t>
-  </si>
-  <si>
-    <t>Amazon com</t>
-  </si>
-  <si>
-    <t>US0231351067</t>
-  </si>
-  <si>
-    <t>Internet &amp; Direct Marketing Retail</t>
-  </si>
-  <si>
     <t>Microsoft Corp</t>
   </si>
   <si>
@@ -550,21 +478,21 @@
     <t>Systems Software</t>
   </si>
   <si>
+    <t>Cognizant Tech Solutions</t>
+  </si>
+  <si>
+    <t>US1924461023</t>
+  </si>
+  <si>
+    <t>It Consulting &amp; Other Services</t>
+  </si>
+  <si>
     <t>Epam Systems Inc</t>
   </si>
   <si>
     <t>US29414B1044</t>
   </si>
   <si>
-    <t>Cognizant Tech Solutions</t>
-  </si>
-  <si>
-    <t>US1924461023</t>
-  </si>
-  <si>
-    <t>It Consulting &amp; Other Services</t>
-  </si>
-  <si>
     <t>Accenture Plc</t>
   </si>
   <si>
@@ -607,28 +535,31 @@
     <t>91 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024X409</t>
+    <t>IN002025X018</t>
   </si>
   <si>
     <t>SOV</t>
   </si>
   <si>
-    <t>IN002024X425</t>
+    <t>IN002024X516</t>
+  </si>
+  <si>
+    <t>IN002025X026</t>
   </si>
   <si>
     <t>182 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024Y191</t>
-  </si>
-  <si>
-    <t>IN002024X417</t>
+    <t>IN002024Y407</t>
   </si>
   <si>
     <t>364 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024Z040</t>
+    <t>IN002024Z164</t>
+  </si>
+  <si>
+    <t>IN002025X034</t>
   </si>
   <si>
     <t>Units of Real Estate Investment Trust (REITs)</t>
@@ -661,16 +592,13 @@
     <t>ICICI Bank Ltd. $$</t>
   </si>
   <si>
-    <t>KEI Industries Ltd. $$</t>
-  </si>
-  <si>
-    <t>HDFC Life Insurance Company Ltd $$</t>
-  </si>
-  <si>
-    <t>PI Industries Ltd. $$</t>
-  </si>
-  <si>
-    <t>Siemens Ltd. $$</t>
+    <t>Avenue Supermarts Ltd. $$</t>
+  </si>
+  <si>
+    <t>Computer Age Management Services Ltd. $$</t>
+  </si>
+  <si>
+    <t>Eternal Ltd. $$</t>
   </si>
   <si>
     <t>Note- 1 : Index/ Stock futures are provided towards end of the table.</t>
@@ -694,7 +622,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -1098,13 +1026,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>155</xdr:row>
+      <xdr:row>146</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>165</xdr:row>
+      <xdr:row>156</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1122,7 +1050,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="29984700"/>
+          <a:off x="666750" y="28270200"/>
           <a:ext cx="3590925" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1137,13 +1065,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>170</xdr:row>
+      <xdr:row>161</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>180</xdr:row>
+      <xdr:row>171</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1161,7 +1089,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="32842200"/>
+          <a:off x="666750" y="31127700"/>
           <a:ext cx="3590925" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1495,15 +1423,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J169"/>
+  <dimension ref="B1:J160"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
     <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="53.857142857142854" collapsed="true"/>
     <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="17.0" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="21" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="35.0" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="11.0" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="34.142857142857146" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="11.142857142857142" collapsed="true"/>
     <col min="7" max="7" bestFit="true" customWidth="true" style="21" width="38.714285714285715" collapsed="true"/>
     <col min="8" max="8" bestFit="true" customWidth="true" style="21" width="11.714285714285714" collapsed="true"/>
     <col min="9" max="9" bestFit="true" customWidth="true" style="21" width="29.714285714285715" collapsed="true"/>
@@ -1595,10 +1523,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>615658.68</v>
+        <v>650340.5200000001</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9577656938069999</v>
+        <v>0.9572687230795</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1632,10 +1560,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>615658.68</v>
+        <v>650340.5200000001</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9577656938069999</v>
+        <v>0.9572687230795</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1669,10 +1597,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="9">
-        <v>578838.3300000001</v>
+        <v>630583.4700000001</v>
       </c>
       <c r="H9" s="10">
-        <v>0.9004851433826999</v>
+        <v>0.9281873334941</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>13</v>
@@ -1695,13 +1623,13 @@
         <v>18</v>
       </c>
       <c r="F10" s="14">
-        <v>2552239</v>
+        <v>3077239</v>
       </c>
       <c r="G10" s="15">
-        <v>31974.45</v>
+        <v>44490.72</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0497418980407</v>
+        <v>0.0654881149392</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1724,13 +1652,13 @@
         <v>21</v>
       </c>
       <c r="F11" s="14">
-        <v>778957</v>
+        <v>2246376</v>
       </c>
       <c r="G11" s="15">
-        <v>22369.31</v>
+        <v>31918.76</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0347994081919</v>
+        <v>0.0469828185203</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1753,13 +1681,13 @@
         <v>24</v>
       </c>
       <c r="F12" s="14">
-        <v>879065</v>
+        <v>863143</v>
       </c>
       <c r="G12" s="15">
-        <v>18288.51</v>
+        <v>26819.58</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0284510038401</v>
+        <v>0.0394770805611</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1779,16 +1707,16 @@
         <v>13</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F13" s="14">
-        <v>1423285</v>
+        <v>2073429</v>
       </c>
       <c r="G13" s="15">
-        <v>18005.98</v>
+        <v>24719.42</v>
       </c>
       <c r="H13" s="16">
-        <v>0.02801147858</v>
+        <v>0.0363857500663</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1799,25 +1727,25 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>30</v>
-      </c>
       <c r="F14" s="14">
-        <v>136835</v>
+        <v>176271</v>
       </c>
       <c r="G14" s="15">
-        <v>16845.28</v>
+        <v>21714.82</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0262058049545</v>
+        <v>0.0319631291209</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1828,25 +1756,25 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1">
       <c r="B15" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="D15" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>24</v>
-      </c>
       <c r="F15" s="14">
-        <v>900218</v>
+        <v>1168119</v>
       </c>
       <c r="G15" s="15">
-        <v>15699.35</v>
+        <v>21682.62</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0244231086697</v>
+        <v>0.0319157323312</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1869,13 +1797,13 @@
         <v>35</v>
       </c>
       <c r="F16" s="14">
-        <v>981750</v>
+        <v>1041840</v>
       </c>
       <c r="G16" s="15">
-        <v>15376.17</v>
+        <v>20396.1</v>
       </c>
       <c r="H16" s="16">
-        <v>0.023920345163</v>
+        <v>0.0300220392277</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1895,16 +1823,16 @@
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F17" s="14">
-        <v>498443</v>
+        <v>655341</v>
       </c>
       <c r="G17" s="15">
-        <v>14902.70</v>
+        <v>19508.19</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0231837790464</v>
+        <v>0.0287150801105</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1924,16 +1852,16 @@
         <v>13</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F18" s="14">
-        <v>1493473</v>
+        <v>1372129</v>
       </c>
       <c r="G18" s="15">
-        <v>14727.14</v>
+        <v>19234.50</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0229106644934</v>
+        <v>0.0283122221173</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1956,13 +1884,13 @@
         <v>42</v>
       </c>
       <c r="F19" s="14">
-        <v>246964</v>
+        <v>1152787</v>
       </c>
       <c r="G19" s="15">
-        <v>14605.82</v>
+        <v>18014.60</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0227219298296</v>
+        <v>0.0265165903223</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1985,13 +1913,13 @@
         <v>45</v>
       </c>
       <c r="F20" s="14">
-        <v>890907</v>
+        <v>474858</v>
       </c>
       <c r="G20" s="15">
-        <v>14488.82</v>
+        <v>17451.51</v>
       </c>
       <c r="H20" s="16">
-        <v>0.022539915688</v>
+        <v>0.0256877500014</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -2011,16 +1939,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F21" s="14">
-        <v>1205822</v>
+        <v>1015785</v>
       </c>
       <c r="G21" s="15">
-        <v>14460.82</v>
+        <v>17040.81</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0224963567481</v>
+        <v>0.0250832201398</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -2040,16 +1968,16 @@
         <v>13</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F22" s="14">
-        <v>586877</v>
+        <v>586527</v>
       </c>
       <c r="G22" s="15">
-        <v>14424.85</v>
+        <v>16310.14</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0224403990671</v>
+        <v>0.0240077104392</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -2072,13 +2000,13 @@
         <v>52</v>
       </c>
       <c r="F23" s="14">
-        <v>403093</v>
+        <v>1230374</v>
       </c>
       <c r="G23" s="15">
-        <v>14379.94</v>
+        <v>15150.83</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0223705336389</v>
+        <v>0.0223012640942</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -2098,16 +2026,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F24" s="14">
-        <v>751182</v>
+        <v>5023558</v>
       </c>
       <c r="G24" s="15">
-        <v>14120.72</v>
+        <v>14555.76</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0219672711962</v>
+        <v>0.0214253508126</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -2118,25 +2046,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="F25" s="14">
-        <v>1216333</v>
+        <v>277414</v>
       </c>
       <c r="G25" s="15">
-        <v>13638.13</v>
+        <v>14061.84</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0212165173107</v>
+        <v>0.0206983252727</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -2156,16 +2084,16 @@
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="F26" s="14">
-        <v>2013619</v>
+        <v>733017</v>
       </c>
       <c r="G26" s="15">
-        <v>12847.90</v>
+        <v>13540.29</v>
       </c>
       <c r="H26" s="16">
-        <v>0.01998717513</v>
+        <v>0.0199306297544</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -2176,25 +2104,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="D27" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>18</v>
-      </c>
       <c r="F27" s="14">
-        <v>755492</v>
+        <v>572968</v>
       </c>
       <c r="G27" s="15">
-        <v>12833.92</v>
+        <v>13455.01</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0199654267736</v>
+        <v>0.0198051018591</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2214,16 +2142,16 @@
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="F28" s="14">
-        <v>517968</v>
+        <v>1139477</v>
       </c>
       <c r="G28" s="15">
-        <v>12787.59</v>
+        <v>13078.92</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0198933522849</v>
+        <v>0.0192515161867</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -2234,25 +2162,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="D29" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>68</v>
-      </c>
       <c r="F29" s="14">
-        <v>435074</v>
+        <v>893260</v>
       </c>
       <c r="G29" s="15">
-        <v>12678.27</v>
+        <v>12751.29</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0197232857382</v>
+        <v>0.0187692612109</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2263,25 +2191,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="D30" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>71</v>
-      </c>
       <c r="F30" s="14">
-        <v>4099958</v>
+        <v>1885976</v>
       </c>
       <c r="G30" s="15">
-        <v>12367.52</v>
+        <v>12193.78</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0192398592894</v>
+        <v>0.017948634371</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2292,25 +2220,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>73</v>
-      </c>
       <c r="D31" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="F31" s="14">
-        <v>201765</v>
+        <v>3565261</v>
       </c>
       <c r="G31" s="15">
-        <v>12253.89</v>
+        <v>11904.41</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0190630877773</v>
+        <v>0.0175226962019</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2321,25 +2249,25 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C32" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>77</v>
-      </c>
       <c r="F32" s="14">
-        <v>156826</v>
+        <v>1523052</v>
       </c>
       <c r="G32" s="15">
-        <v>12112.77</v>
+        <v>11831.83</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0188435507203</v>
+        <v>0.0174158620715</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2350,25 +2278,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="F33" s="14">
-        <v>321234</v>
+        <v>273124</v>
       </c>
       <c r="G33" s="15">
-        <v>11772.10</v>
+        <v>10930.70</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0183135784329</v>
+        <v>0.0160894437753</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2379,25 +2307,25 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="F34" s="14">
-        <v>1501140</v>
+        <v>191571</v>
       </c>
       <c r="G34" s="15">
-        <v>11208.26</v>
+        <v>10811.31</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0174364258379</v>
+        <v>0.0159137076658</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2408,25 +2336,25 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="F35" s="14">
-        <v>1063214</v>
+        <v>169666</v>
       </c>
       <c r="G35" s="15">
-        <v>10315.83</v>
+        <v>10130.76</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0160480935267</v>
+        <v>0.0149119720989</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2437,25 +2365,25 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="F36" s="14">
-        <v>3140806</v>
+        <v>1076714</v>
       </c>
       <c r="G36" s="15">
-        <v>10176.21</v>
+        <v>10013.44</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0158308899843</v>
+        <v>0.0147392829259</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2466,25 +2394,25 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C37" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>74</v>
-      </c>
       <c r="F37" s="14">
-        <v>169666</v>
+        <v>271168</v>
       </c>
       <c r="G37" s="15">
-        <v>9967.28</v>
+        <v>9789.71</v>
       </c>
       <c r="H37" s="16">
-        <v>0.015505862509</v>
+        <v>0.0144099635542</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2495,25 +2423,25 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C38" s="13" t="s">
-        <v>90</v>
-      </c>
       <c r="D38" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="F38" s="14">
-        <v>171805</v>
+        <v>494438</v>
       </c>
       <c r="G38" s="15">
-        <v>9884.29</v>
+        <v>9616.32</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0153767569226</v>
+        <v>0.0141547421451</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2524,25 +2452,25 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="D39" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="D39" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>93</v>
-      </c>
       <c r="F39" s="14">
-        <v>411545</v>
+        <v>24227783</v>
       </c>
       <c r="G39" s="15">
-        <v>9519.86</v>
+        <v>9577.24</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0148098217633</v>
+        <v>0.0140972183394</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -2553,25 +2481,25 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>95</v>
-      </c>
       <c r="D40" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="F40" s="14">
-        <v>798172</v>
+        <v>284563</v>
       </c>
       <c r="G40" s="15">
-        <v>9353.78</v>
+        <v>9299.8</v>
       </c>
       <c r="H40" s="16">
-        <v>0.0145514550228</v>
+        <v>0.0136888405337</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -2582,25 +2510,25 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C41" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="D41" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D41" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>21</v>
-      </c>
       <c r="F41" s="14">
-        <v>246569</v>
+        <v>2073250</v>
       </c>
       <c r="G41" s="15">
-        <v>6928.22</v>
+        <v>8848.63</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0107780685154</v>
+        <v>0.0130247408559</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -2620,16 +2548,16 @@
         <v>13</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F42" s="14">
-        <v>174385</v>
+        <v>3395146</v>
       </c>
       <c r="G42" s="15">
-        <v>6920.99</v>
+        <v>8090.97</v>
       </c>
       <c r="H42" s="16">
-        <v>0.0107668209749</v>
+        <v>0.0119095032251</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -2649,16 +2577,16 @@
         <v>13</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="F43" s="14">
-        <v>406137</v>
+        <v>782788</v>
       </c>
       <c r="G43" s="15">
-        <v>6797.31</v>
+        <v>7807.92</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0105744149147</v>
+        <v>0.0114928677799</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -2669,25 +2597,25 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C44" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>24</v>
-      </c>
       <c r="F44" s="14">
-        <v>92907</v>
+        <v>1032512</v>
       </c>
       <c r="G44" s="15">
-        <v>6721.91</v>
+        <v>7713.38</v>
       </c>
       <c r="H44" s="16">
-        <v>0.0104571169123</v>
+        <v>0.0113537096277</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -2698,25 +2626,25 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D45" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="F45" s="14">
-        <v>1120000</v>
+        <v>406137</v>
       </c>
       <c r="G45" s="15">
-        <v>6656.16</v>
+        <v>7486.73</v>
       </c>
       <c r="H45" s="16">
-        <v>0.0103548311874</v>
+        <v>0.0110200921621</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -2736,16 +2664,16 @@
         <v>13</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="F46" s="14">
-        <v>589218</v>
+        <v>224890</v>
       </c>
       <c r="G46" s="15">
-        <v>6574.20</v>
+        <v>7344.01</v>
       </c>
       <c r="H46" s="16">
-        <v>0.0102273279477</v>
+        <v>0.0108100154592</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>13</v>
@@ -2765,16 +2693,16 @@
         <v>13</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="F47" s="14">
-        <v>13175131</v>
+        <v>174385</v>
       </c>
       <c r="G47" s="15">
-        <v>6536.18</v>
+        <v>7230.35</v>
       </c>
       <c r="H47" s="16">
-        <v>0.0101681811301</v>
+        <v>0.0106427136232</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>13</v>
@@ -2785,25 +2713,25 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C48" s="13" t="s">
-        <v>113</v>
-      </c>
       <c r="D48" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="F48" s="14">
-        <v>161118</v>
+        <v>1219795</v>
       </c>
       <c r="G48" s="15">
-        <v>6482.74</v>
+        <v>5891</v>
       </c>
       <c r="H48" s="16">
-        <v>0.010085045782</v>
+        <v>0.0086712574017</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>13</v>
@@ -2814,25 +2742,25 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C49" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="C49" s="13" t="s">
-        <v>115</v>
-      </c>
       <c r="D49" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="F49" s="14">
-        <v>1160999</v>
+        <v>224890</v>
       </c>
       <c r="G49" s="15">
-        <v>6151.55</v>
+        <v>5573.11</v>
       </c>
       <c r="H49" s="16">
-        <v>0.009569821307</v>
+        <v>0.0082033392188</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>13</v>
@@ -2843,25 +2771,25 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C50" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="C50" s="13" t="s">
-        <v>117</v>
-      </c>
       <c r="D50" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F50" s="14">
-        <v>112500</v>
+        <v>1356000</v>
       </c>
       <c r="G50" s="15">
-        <v>5843.59</v>
+        <v>5430.78</v>
       </c>
       <c r="H50" s="16">
-        <v>0.0090907351955</v>
+        <v>0.0079938365764</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>13</v>
@@ -2872,25 +2800,25 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C51" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="D51" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="D51" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>120</v>
-      </c>
       <c r="F51" s="14">
-        <v>2527089</v>
+        <v>3500036</v>
       </c>
       <c r="G51" s="15">
-        <v>5437.03</v>
+        <v>5359.26</v>
       </c>
       <c r="H51" s="16">
-        <v>0.0084582593884</v>
+        <v>0.007888562713</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>13</v>
@@ -2901,25 +2829,25 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="C52" s="13" t="s">
-        <v>122</v>
-      </c>
       <c r="D52" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="F52" s="14">
-        <v>123755</v>
+        <v>8076080</v>
       </c>
       <c r="G52" s="15">
-        <v>5134.22</v>
+        <v>4674.44</v>
       </c>
       <c r="H52" s="16">
-        <v>0.0079871850104</v>
+        <v>0.0068805419196</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>13</v>
@@ -2930,25 +2858,25 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C53" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="C53" s="13" t="s">
-        <v>124</v>
-      </c>
       <c r="D53" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="F53" s="14">
-        <v>89991</v>
+        <v>540374</v>
       </c>
       <c r="G53" s="15">
-        <v>5019.43</v>
+        <v>4572.64</v>
       </c>
       <c r="H53" s="16">
-        <v>0.0078086089137</v>
+        <v>0.0067306974105</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>13</v>
@@ -2959,25 +2887,25 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C54" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="C54" s="13" t="s">
-        <v>126</v>
-      </c>
       <c r="D54" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F54" s="14">
-        <v>368720</v>
+        <v>937773</v>
       </c>
       <c r="G54" s="15">
-        <v>4781.56</v>
+        <v>4479.27</v>
       </c>
       <c r="H54" s="16">
-        <v>0.0074385601627</v>
+        <v>0.0065932614397</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>13</v>
@@ -2988,25 +2916,25 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="C55" s="13" t="s">
-        <v>128</v>
-      </c>
       <c r="D55" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F55" s="14">
-        <v>4414668</v>
+        <v>1547683</v>
       </c>
       <c r="G55" s="15">
-        <v>4765.63</v>
+        <v>4078.92</v>
       </c>
       <c r="H55" s="16">
-        <v>0.0074137782373</v>
+        <v>0.0060039662605</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>13</v>
@@ -3017,25 +2945,25 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C56" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="C56" s="13" t="s">
-        <v>130</v>
-      </c>
       <c r="D56" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>131</v>
+        <v>45</v>
       </c>
       <c r="F56" s="14">
-        <v>3292664</v>
+        <v>355355</v>
       </c>
       <c r="G56" s="15">
-        <v>4651.22</v>
+        <v>4046.61</v>
       </c>
       <c r="H56" s="16">
-        <v>0.0072357932976</v>
+        <v>0.0059564075563</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>13</v>
@@ -3046,25 +2974,25 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D57" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="F57" s="14">
-        <v>33971</v>
+        <v>98500</v>
       </c>
       <c r="G57" s="15">
-        <v>4369.88</v>
+        <v>3901.68</v>
       </c>
       <c r="H57" s="16">
-        <v>0.0067981192924</v>
+        <v>0.005743077844</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>13</v>
@@ -3075,25 +3003,25 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D58" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="F58" s="14">
-        <v>937773</v>
+        <v>100000</v>
       </c>
       <c r="G58" s="15">
-        <v>4062.90</v>
+        <v>3497.90</v>
       </c>
       <c r="H58" s="16">
-        <v>0.0063205577437</v>
+        <v>0.0051487338763</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>13</v>
@@ -3104,25 +3032,25 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D59" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F59" s="14">
-        <v>355355</v>
+        <v>787042</v>
       </c>
       <c r="G59" s="15">
-        <v>3761.97</v>
+        <v>3290.23</v>
       </c>
       <c r="H59" s="16">
-        <v>0.0058524080374</v>
+        <v>0.0048430540215</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>13</v>
@@ -3133,25 +3061,25 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C60" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>74</v>
-      </c>
       <c r="F60" s="14">
-        <v>199637</v>
+        <v>293545</v>
       </c>
       <c r="G60" s="15">
-        <v>3568.51</v>
+        <v>3212.56</v>
       </c>
       <c r="H60" s="16">
-        <v>0.0055514468764</v>
+        <v>0.0047287276656</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>13</v>
@@ -3162,25 +3090,25 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
       <c r="B61" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C61" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C61" s="13" t="s">
+      <c r="D61" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="D61" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E61" s="13" t="s">
-        <v>68</v>
-      </c>
       <c r="F61" s="14">
-        <v>494775</v>
+        <v>191387</v>
       </c>
       <c r="G61" s="15">
-        <v>3476.04</v>
+        <v>2922.48</v>
       </c>
       <c r="H61" s="16">
-        <v>0.0054075934774</v>
+        <v>0.004301744412</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>13</v>
@@ -3200,16 +3128,16 @@
         <v>13</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>71</v>
+        <v>144</v>
       </c>
       <c r="F62" s="14">
-        <v>4128493</v>
+        <v>2100329</v>
       </c>
       <c r="G62" s="15">
-        <v>3325.50</v>
+        <v>2098.44</v>
       </c>
       <c r="H62" s="16">
-        <v>0.0051734019485</v>
+        <v>0.0030887987407</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>13</v>
@@ -3220,25 +3148,25 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F63" s="14">
-        <v>81524</v>
+        <v>149356</v>
       </c>
       <c r="G63" s="15">
-        <v>3209.44</v>
+        <v>877.17</v>
       </c>
       <c r="H63" s="16">
-        <v>0.0049928501427</v>
+        <v>0.0012911503743</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>13</v>
@@ -3249,25 +3177,25 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D64" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="F64" s="14">
-        <v>615525</v>
+        <v>16762</v>
       </c>
       <c r="G64" s="15">
-        <v>3118.25</v>
+        <v>159.98</v>
       </c>
       <c r="H64" s="16">
-        <v>0.0048509880096</v>
+        <v>0.0002354825596</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>13</v>
@@ -3278,56 +3206,35 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J65" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" ht="15" customHeight="1">
+      <c r="B66" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C65" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="D65" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="F65" s="14">
-        <v>448854</v>
-      </c>
-      <c r="G65" s="15">
-        <v>3065.22</v>
-      </c>
-      <c r="H65" s="16">
-        <v>0.0047684904888</v>
-      </c>
-      <c r="I65" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J65" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10" ht="15" customHeight="1">
-      <c r="B66" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="C66" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="D66" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E66" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F66" s="14">
-        <v>416789</v>
-      </c>
-      <c r="G66" s="15">
-        <v>2920.02</v>
-      </c>
-      <c r="H66" s="16">
-        <v>0.004542606272</v>
-      </c>
-      <c r="I66" s="15" t="s">
+      <c r="C66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" s="9">
+        <v>19757.05</v>
+      </c>
+      <c r="H66" s="10">
+        <v>0.0290813895854</v>
+      </c>
+      <c r="I66" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J66" s="11" t="s">
@@ -3336,25 +3243,25 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D67" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="F67" s="14">
-        <v>151539</v>
+        <v>17772</v>
       </c>
       <c r="G67" s="15">
-        <v>2718.69</v>
+        <v>6993.38</v>
       </c>
       <c r="H67" s="16">
-        <v>0.0042294019376</v>
+        <v>0.0102939056336</v>
       </c>
       <c r="I67" s="15" t="s">
         <v>13</v>
@@ -3365,25 +3272,25 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F68" s="14">
-        <v>65438</v>
+        <v>81355</v>
       </c>
       <c r="G68" s="15">
-        <v>2279.7</v>
+        <v>5632.08</v>
       </c>
       <c r="H68" s="16">
-        <v>0.0035464755441</v>
+        <v>0.0082901401098</v>
       </c>
       <c r="I68" s="15" t="s">
         <v>13</v>
@@ -3394,25 +3301,25 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="12" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>162</v>
+        <v>92</v>
       </c>
       <c r="F69" s="14">
-        <v>2100329</v>
+        <v>28603</v>
       </c>
       <c r="G69" s="15">
-        <v>1993.84</v>
+        <v>4266.14</v>
       </c>
       <c r="H69" s="16">
-        <v>0.0031017698815</v>
+        <v>0.006279544738</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>13</v>
@@ -3423,25 +3330,25 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="12" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="F70" s="14">
-        <v>313348</v>
+        <v>10581</v>
       </c>
       <c r="G70" s="15">
-        <v>1985.06</v>
+        <v>2865.45</v>
       </c>
       <c r="H70" s="16">
-        <v>0.0030881110425</v>
+        <v>0.004217799104</v>
       </c>
       <c r="I70" s="15" t="s">
         <v>13</v>
@@ -3452,27 +3359,6 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="C71" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="D71" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="F71" s="14">
-        <v>244579</v>
-      </c>
-      <c r="G71" s="15">
-        <v>1193.91</v>
-      </c>
-      <c r="H71" s="16">
-        <v>0.0018573376395</v>
-      </c>
-      <c r="I71" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J71" s="11" t="s">
@@ -3480,7 +3366,28 @@
       </c>
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
-      <c r="B72" s="12" t="s">
+      <c r="B72" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H72" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I72" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J72" s="11" t="s">
@@ -3488,28 +3395,7 @@
       </c>
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
-      <c r="B73" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G73" s="9">
-        <v>36820.350000000006</v>
-      </c>
-      <c r="H73" s="10">
-        <v>0.0572805504243</v>
-      </c>
-      <c r="I73" s="9" t="s">
+      <c r="B73" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J73" s="11" t="s">
@@ -3517,28 +3403,28 @@
       </c>
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1">
-      <c r="B74" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E74" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="F74" s="14">
-        <v>55891</v>
-      </c>
-      <c r="G74" s="15">
-        <v>8235.11</v>
-      </c>
-      <c r="H74" s="16">
-        <v>0.0128111664774</v>
-      </c>
-      <c r="I74" s="15" t="s">
+      <c r="B74" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H74" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I74" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J74" s="11" t="s">
@@ -3547,27 +3433,6 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
       <c r="B75" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="C75" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="D75" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E75" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="F75" s="14">
-        <v>31800</v>
-      </c>
-      <c r="G75" s="15">
-        <v>6548.55</v>
-      </c>
-      <c r="H75" s="16">
-        <v>0.0101874248474</v>
-      </c>
-      <c r="I75" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J75" s="11" t="s">
@@ -3575,28 +3440,28 @@
       </c>
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
-      <c r="B76" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="C76" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="D76" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="F76" s="14">
-        <v>17772</v>
-      </c>
-      <c r="G76" s="15">
-        <v>6391.06</v>
-      </c>
-      <c r="H76" s="16">
-        <v>0.0099424213674</v>
-      </c>
-      <c r="I76" s="15" t="s">
+      <c r="B76" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I76" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J76" s="11" t="s">
@@ -3605,27 +3470,6 @@
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1">
       <c r="B77" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="C77" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="D77" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E77" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="F77" s="14">
-        <v>28603</v>
-      </c>
-      <c r="G77" s="15">
-        <v>6293.65</v>
-      </c>
-      <c r="H77" s="16">
-        <v>0.0097908829269</v>
-      </c>
-      <c r="I77" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J77" s="11" t="s">
@@ -3633,28 +3477,28 @@
       </c>
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
-      <c r="B78" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="C78" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="D78" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E78" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="F78" s="14">
-        <v>81355</v>
-      </c>
-      <c r="G78" s="15">
-        <v>5822.94</v>
-      </c>
-      <c r="H78" s="16">
-        <v>0.0090586104773</v>
-      </c>
-      <c r="I78" s="15" t="s">
+      <c r="B78" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H78" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I78" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J78" s="11" t="s">
@@ -3663,27 +3507,6 @@
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1">
       <c r="B79" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="C79" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="D79" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E79" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="F79" s="14">
-        <v>10581</v>
-      </c>
-      <c r="G79" s="15">
-        <v>3529.04</v>
-      </c>
-      <c r="H79" s="16">
-        <v>0.0054900443279</v>
-      </c>
-      <c r="I79" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J79" s="11" t="s">
@@ -3691,7 +3514,28 @@
       </c>
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H80" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I80" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J80" s="11" t="s">
@@ -3699,28 +3543,7 @@
       </c>
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1">
-      <c r="B81" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I81" s="9" t="s">
+      <c r="B81" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J81" s="11" t="s">
@@ -3728,7 +3551,28 @@
       </c>
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1">
-      <c r="B82" s="12" t="s">
+      <c r="B82" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I82" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J82" s="11" t="s">
@@ -3736,28 +3580,7 @@
       </c>
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1">
-      <c r="B83" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I83" s="9" t="s">
+      <c r="B83" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J83" s="11" t="s">
@@ -3765,7 +3588,28 @@
       </c>
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1">
-      <c r="B84" s="12" t="s">
+      <c r="B84" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I84" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J84" s="11" t="s">
@@ -3773,28 +3617,7 @@
       </c>
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1">
-      <c r="B85" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G85" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I85" s="9" t="s">
+      <c r="B85" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J85" s="11" t="s">
@@ -3802,7 +3625,28 @@
       </c>
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1">
-      <c r="B86" s="12" t="s">
+      <c r="B86" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="9">
+        <v>14021.03</v>
+      </c>
+      <c r="H86" s="10">
+        <v>0.0206382549933</v>
+      </c>
+      <c r="I86" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J86" s="11" t="s">
@@ -3810,28 +3654,7 @@
       </c>
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1">
-      <c r="B87" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E87" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I87" s="9" t="s">
+      <c r="B87" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J87" s="11" t="s">
@@ -3839,7 +3662,28 @@
       </c>
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1">
-      <c r="B88" s="12" t="s">
+      <c r="B88" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H88" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I88" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J88" s="11" t="s">
@@ -3847,28 +3691,7 @@
       </c>
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1">
-      <c r="B89" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I89" s="9" t="s">
+      <c r="B89" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J89" s="11" t="s">
@@ -3876,7 +3699,28 @@
       </c>
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1">
-      <c r="B90" s="12" t="s">
+      <c r="B90" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H90" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I90" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J90" s="11" t="s">
@@ -3884,28 +3728,7 @@
       </c>
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1">
-      <c r="B91" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G91" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I91" s="9" t="s">
+      <c r="B91" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J91" s="11" t="s">
@@ -3913,7 +3736,28 @@
       </c>
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1">
-      <c r="B92" s="12" t="s">
+      <c r="B92" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G92" s="9">
+        <v>14021.03</v>
+      </c>
+      <c r="H92" s="10">
+        <v>0.0206382549933</v>
+      </c>
+      <c r="I92" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J92" s="11" t="s">
@@ -3921,29 +3765,29 @@
       </c>
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1">
-      <c r="B93" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E93" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F93" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G93" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I93" s="9" t="s">
-        <v>13</v>
+      <c r="B93" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="D93" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="F93" s="14">
+        <v>5000000</v>
+      </c>
+      <c r="G93" s="15">
+        <v>4975.47</v>
+      </c>
+      <c r="H93" s="16">
+        <v>0.0073236430257</v>
+      </c>
+      <c r="I93" s="15">
+        <v>5.62</v>
       </c>
       <c r="J93" s="11" t="s">
         <v>13</v>
@@ -3951,36 +3795,57 @@
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1">
       <c r="B94" s="12" t="s">
-        <v>13</v>
+        <v>172</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="F94" s="14">
+        <v>2400000</v>
+      </c>
+      <c r="G94" s="15">
+        <v>2390.67</v>
+      </c>
+      <c r="H94" s="16">
+        <v>0.0035189466869</v>
+      </c>
+      <c r="I94" s="15">
+        <v>5.70</v>
       </c>
       <c r="J94" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1">
-      <c r="B95" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F95" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G95" s="9">
-        <v>11474.319999999998</v>
-      </c>
-      <c r="H95" s="10">
-        <v>0.0178503291071</v>
-      </c>
-      <c r="I95" s="9" t="s">
-        <v>13</v>
+      <c r="B95" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="F95" s="14">
+        <v>2400000</v>
+      </c>
+      <c r="G95" s="15">
+        <v>2385.36</v>
+      </c>
+      <c r="H95" s="16">
+        <v>0.0035111306324</v>
+      </c>
+      <c r="I95" s="15">
+        <v>5.60</v>
       </c>
       <c r="J95" s="11" t="s">
         <v>13</v>
@@ -3988,36 +3853,57 @@
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1">
       <c r="B96" s="12" t="s">
-        <v>13</v>
+        <v>177</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="F96" s="14">
+        <v>2250000</v>
+      </c>
+      <c r="G96" s="15">
+        <v>2234.2</v>
+      </c>
+      <c r="H96" s="16">
+        <v>0.0032886306716</v>
+      </c>
+      <c r="I96" s="15">
+        <v>5.61</v>
       </c>
       <c r="J96" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1">
-      <c r="B97" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D97" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E97" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F97" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G97" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I97" s="9" t="s">
-        <v>13</v>
+      <c r="B97" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="D97" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="F97" s="14">
+        <v>1800000</v>
+      </c>
+      <c r="G97" s="15">
+        <v>1787.09</v>
+      </c>
+      <c r="H97" s="16">
+        <v>0.0026305071108</v>
+      </c>
+      <c r="I97" s="15">
+        <v>5.61</v>
       </c>
       <c r="J97" s="11" t="s">
         <v>13</v>
@@ -4025,35 +3911,35 @@
     </row>
     <row r="98" spans="2:10" ht="15" customHeight="1">
       <c r="B98" s="12" t="s">
-        <v>13</v>
+        <v>172</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E98" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="F98" s="14">
+        <v>250000</v>
+      </c>
+      <c r="G98" s="15">
+        <v>248.24</v>
+      </c>
+      <c r="H98" s="16">
+        <v>0.0003653968659</v>
+      </c>
+      <c r="I98" s="15">
+        <v>5.61</v>
       </c>
       <c r="J98" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1">
-      <c r="B99" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E99" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F99" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G99" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I99" s="9" t="s">
+      <c r="B99" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J99" s="11" t="s">
@@ -4061,7 +3947,28 @@
       </c>
     </row>
     <row r="100" spans="2:10" ht="15" customHeight="1">
-      <c r="B100" s="12" t="s">
+      <c r="B100" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H100" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I100" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J100" s="11" t="s">
@@ -4069,28 +3976,7 @@
       </c>
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1">
-      <c r="B101" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D101" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E101" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F101" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G101" s="9">
-        <v>11474.319999999998</v>
-      </c>
-      <c r="H101" s="10">
-        <v>0.0178503291071</v>
-      </c>
-      <c r="I101" s="9" t="s">
+      <c r="B101" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J101" s="11" t="s">
@@ -4098,29 +3984,29 @@
       </c>
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1">
-      <c r="B102" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="C102" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="D102" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E102" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="F102" s="14">
-        <v>5000000</v>
-      </c>
-      <c r="G102" s="15">
-        <v>4939.98</v>
-      </c>
-      <c r="H102" s="16">
-        <v>0.0076850104218</v>
-      </c>
-      <c r="I102" s="15">
-        <v>6.52</v>
+      <c r="B102" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D102" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F102" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G102" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H102" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I102" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J102" s="11" t="s">
         <v>13</v>
@@ -4128,57 +4014,36 @@
     </row>
     <row r="103" spans="2:10" ht="15" customHeight="1">
       <c r="B103" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="C103" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="D103" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E103" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="F103" s="14">
-        <v>2500000</v>
-      </c>
-      <c r="G103" s="15">
-        <v>2463.95</v>
-      </c>
-      <c r="H103" s="16">
-        <v>0.0038331089253</v>
-      </c>
-      <c r="I103" s="15">
-        <v>6.51</v>
+        <v>13</v>
       </c>
       <c r="J103" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="104" spans="2:10" ht="15" customHeight="1">
-      <c r="B104" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="C104" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="D104" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E104" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="F104" s="14">
-        <v>2000000</v>
-      </c>
-      <c r="G104" s="15">
-        <v>1998.26</v>
-      </c>
-      <c r="H104" s="16">
-        <v>0.0031086459713</v>
-      </c>
-      <c r="I104" s="15">
-        <v>6.37</v>
+      <c r="B104" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F104" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G104" s="9">
+        <v>18108.53</v>
+      </c>
+      <c r="H104" s="10">
+        <v>0.026654850585</v>
+      </c>
+      <c r="I104" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J104" s="11" t="s">
         <v>13</v>
@@ -4186,57 +4051,36 @@
     </row>
     <row r="105" spans="2:10" ht="15" customHeight="1">
       <c r="B105" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="C105" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="D105" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E105" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="F105" s="14">
-        <v>2000000</v>
-      </c>
-      <c r="G105" s="15">
-        <v>1973.57</v>
-      </c>
-      <c r="H105" s="16">
-        <v>0.0030702363204</v>
-      </c>
-      <c r="I105" s="15">
-        <v>6.52</v>
+        <v>13</v>
       </c>
       <c r="J105" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="106" spans="2:10" ht="15" customHeight="1">
-      <c r="B106" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="C106" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="D106" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E106" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="F106" s="14">
-        <v>100000</v>
-      </c>
-      <c r="G106" s="15">
-        <v>98.56</v>
-      </c>
-      <c r="H106" s="16">
-        <v>0.0001533274683</v>
-      </c>
-      <c r="I106" s="15">
-        <v>6.51</v>
+      <c r="B106" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F106" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106" s="9">
+        <v>1719</v>
+      </c>
+      <c r="H106" s="10">
+        <v>0.0025302820359</v>
+      </c>
+      <c r="I106" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J106" s="11" t="s">
         <v>13</v>
@@ -4244,6 +4088,20 @@
     </row>
     <row r="107" spans="2:10" ht="15" customHeight="1">
       <c r="B107" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C107" s="13"/>
+      <c r="D107" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" s="13"/>
+      <c r="G107" s="15">
+        <v>1719</v>
+      </c>
+      <c r="H107" s="16">
+        <v>0.0025302820359</v>
+      </c>
+      <c r="I107" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J107" s="11" t="s">
@@ -4251,28 +4109,7 @@
       </c>
     </row>
     <row r="108" spans="2:10" ht="15" customHeight="1">
-      <c r="B108" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C108" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D108" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E108" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F108" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G108" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H108" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I108" s="9" t="s">
+      <c r="B108" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J108" s="11" t="s">
@@ -4280,130 +4117,151 @@
       </c>
     </row>
     <row r="109" spans="2:10" ht="15" customHeight="1">
-      <c r="B109" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J109" s="11" t="s">
+      <c r="B109" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="C109" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D109" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E109" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F109" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G109" s="18">
+        <v>-4818.173672090052</v>
+      </c>
+      <c r="H109" s="19">
+        <v>-0.007092110697134383</v>
+      </c>
+      <c r="I109" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J109" s="20" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1">
-      <c r="B110" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D110" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E110" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F110" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G110" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H110" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I110" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J110" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="111" spans="2:10" ht="15" customHeight="1">
-      <c r="B111" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J111" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="112" spans="2:10" ht="15" customHeight="1">
-      <c r="B112" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D112" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E112" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F112" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G112" s="9">
-        <v>8891.35</v>
-      </c>
-      <c r="H112" s="10">
-        <v>0.013832063574</v>
-      </c>
-      <c r="I112" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J112" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="113" spans="2:10" ht="15" customHeight="1">
-      <c r="B113" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J113" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="114" spans="2:10" ht="15" customHeight="1">
+      <c r="B110" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="C110" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D110" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E110" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F110" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G110" s="18">
+        <v>679370.90632791</v>
+      </c>
+      <c r="H110" s="19">
+        <v>0.9999999999965657</v>
+      </c>
+      <c r="I110" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J110" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="112" spans="2:8" ht="15" customHeight="1">
+      <c r="B112" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="C112" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D112" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E112" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F112" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G112" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H112" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="113" spans="2:8" ht="15" customHeight="1">
+      <c r="B113" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C113" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D113" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E113" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F113" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G113" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="H113" s="18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114" spans="2:8" ht="15" customHeight="1">
       <c r="B114" s="7" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="C114" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D114" s="9" t="s">
+      <c r="D114" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E114" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F114" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G114" s="9">
-        <v>719</v>
-      </c>
-      <c r="H114" s="10">
-        <v>0.0011185313489</v>
-      </c>
-      <c r="I114" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J114" s="11" t="s">
+      <c r="F114" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G114" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H114" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="115" spans="2:10" ht="15" customHeight="1">
       <c r="B115" s="12" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="C115" s="13"/>
       <c r="D115" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E115" s="13"/>
+      <c r="E115" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F115" s="14">
+        <v>449400</v>
+      </c>
       <c r="G115" s="15">
-        <v>719</v>
+        <v>6540.12</v>
       </c>
       <c r="H115" s="16">
-        <v>0.0011185313489</v>
+        <v>0.0096267295803</v>
       </c>
       <c r="I115" s="15" t="s">
         <v>13</v>
@@ -4414,6 +4272,25 @@
     </row>
     <row r="116" spans="2:10" ht="15" customHeight="1">
       <c r="B116" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="C116" s="13"/>
+      <c r="D116" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="F116" s="14">
+        <v>90000</v>
+      </c>
+      <c r="G116" s="15">
+        <v>3622.14</v>
+      </c>
+      <c r="H116" s="16">
+        <v>0.0053316089433</v>
+      </c>
+      <c r="I116" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J116" s="11" t="s">
@@ -4421,305 +4298,164 @@
       </c>
     </row>
     <row r="117" spans="2:10" ht="15" customHeight="1">
-      <c r="B117" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="C117" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D117" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E117" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F117" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G117" s="18">
-        <v>6063.845933879842</v>
-      </c>
-      <c r="H117" s="19">
-        <v>0.009433382159125016</v>
-      </c>
-      <c r="I117" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J117" s="20" t="s">
+      <c r="B117" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C117" s="13"/>
+      <c r="D117" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E117" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F117" s="14">
+        <v>62500</v>
+      </c>
+      <c r="G117" s="15">
+        <v>2485.63</v>
+      </c>
+      <c r="H117" s="16">
+        <v>0.0036587230581</v>
+      </c>
+      <c r="I117" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J117" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="118" spans="2:10" ht="15" customHeight="1">
-      <c r="B118" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="C118" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D118" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E118" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F118" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G118" s="18">
-        <v>642807.19593388</v>
-      </c>
-      <c r="H118" s="19">
-        <v>0.9999999999961253</v>
-      </c>
-      <c r="I118" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J118" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="120" spans="2:8" ht="15" customHeight="1">
-      <c r="B120" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="C120" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D120" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E120" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F120" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G120" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="H120" s="18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="121" spans="2:8" ht="15" customHeight="1">
-      <c r="B121" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C121" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="D121" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="E121" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F121" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="G121" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="H121" s="18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="122" spans="2:8" ht="15" customHeight="1">
-      <c r="B122" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="C122" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D122" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E122" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F122" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G122" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H122" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="123" spans="2:10" ht="15" customHeight="1">
-      <c r="B123" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="C123" s="13"/>
-      <c r="D123" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E123" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F123" s="14">
-        <v>588700</v>
-      </c>
-      <c r="G123" s="15">
-        <v>7402.610000000001</v>
-      </c>
-      <c r="H123" s="16">
-        <v>0.0115160658543</v>
-      </c>
-      <c r="I123" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J123" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="124" spans="2:10" ht="15" customHeight="1">
-      <c r="B124" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="C124" s="13"/>
-      <c r="D124" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E124" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="F124" s="14">
-        <v>15000</v>
-      </c>
-      <c r="G124" s="15">
-        <v>605.29</v>
-      </c>
-      <c r="H124" s="16">
-        <v>0.0009416353827</v>
-      </c>
-      <c r="I124" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J124" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="125" spans="2:10" ht="15" customHeight="1">
-      <c r="B125" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="C125" s="13"/>
-      <c r="D125" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E125" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F125" s="14">
-        <v>23100</v>
-      </c>
-      <c r="G125" s="15">
-        <v>148.05</v>
-      </c>
-      <c r="H125" s="16">
-        <v>0.0002303178945</v>
-      </c>
-      <c r="I125" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J125" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="126" spans="2:10" ht="15" customHeight="1">
-      <c r="B126" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="C126" s="13"/>
-      <c r="D126" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E126" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="F126" s="14">
-        <v>-30000</v>
-      </c>
-      <c r="G126" s="15">
-        <v>-1049.21</v>
-      </c>
-      <c r="H126" s="16">
-        <v>-0.001632231261</v>
-      </c>
-      <c r="I126" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J126" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="127" spans="2:10" ht="15" customHeight="1">
-      <c r="B127" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="C127" s="13"/>
-      <c r="D127" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E127" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F127" s="14">
-        <v>-39375</v>
-      </c>
-      <c r="G127" s="15">
-        <v>-2401.48</v>
-      </c>
-      <c r="H127" s="16">
-        <v>-0.0037359258191</v>
-      </c>
-      <c r="I127" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J127" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="131" spans="2:9" ht="15" customHeight="1">
-      <c r="B131" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="C131" s="21"/>
-      <c r="D131" s="21"/>
-      <c r="E131" s="21"/>
-      <c r="F131" s="21"/>
-      <c r="G131" s="21"/>
-      <c r="H131" s="21"/>
-      <c r="I131" s="21"/>
-    </row>
-    <row r="135" spans="2:9" ht="15" customHeight="1">
-      <c r="B135" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="C135" s="21"/>
-      <c r="D135" s="21"/>
-      <c r="E135" s="21"/>
-      <c r="F135" s="21"/>
-      <c r="G135" s="21"/>
-      <c r="H135" s="21"/>
-      <c r="I135" s="21"/>
-    </row>
-    <row r="136" spans="2:8" ht="15" customHeight="1">
-      <c r="B136" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="C136" s="21"/>
-      <c r="D136" s="21"/>
-      <c r="E136" s="21"/>
-      <c r="F136" s="21"/>
-      <c r="G136" s="21"/>
-      <c r="H136" s="21"/>
+      <c r="B118" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="C118" s="13"/>
+      <c r="D118" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E118" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="F118" s="14">
+        <v>1000000</v>
+      </c>
+      <c r="G118" s="15">
+        <v>2399.10</v>
+      </c>
+      <c r="H118" s="16">
+        <v>0.0035313552253</v>
+      </c>
+      <c r="I118" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J118" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="122" spans="2:9" ht="15" customHeight="1">
+      <c r="B122" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="C122" s="21"/>
+      <c r="D122" s="21"/>
+      <c r="E122" s="21"/>
+      <c r="F122" s="21"/>
+      <c r="G122" s="21"/>
+      <c r="H122" s="21"/>
+      <c r="I122" s="21"/>
+    </row>
+    <row r="126" spans="2:9" ht="15" customHeight="1">
+      <c r="B126" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="C126" s="21"/>
+      <c r="D126" s="21"/>
+      <c r="E126" s="21"/>
+      <c r="F126" s="21"/>
+      <c r="G126" s="21"/>
+      <c r="H126" s="21"/>
+      <c r="I126" s="21"/>
+    </row>
+    <row r="127" spans="2:8" ht="15" customHeight="1">
+      <c r="B127" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C127" s="21"/>
+      <c r="D127" s="21"/>
+      <c r="E127" s="21"/>
+      <c r="F127" s="21"/>
+      <c r="G127" s="21"/>
+      <c r="H127" s="21"/>
+    </row>
+    <row r="129" spans="2:8" ht="15" customHeight="1">
+      <c r="B129" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="C129" s="21"/>
+      <c r="D129" s="21"/>
+      <c r="E129" s="21"/>
+      <c r="F129" s="21"/>
+      <c r="G129" s="21"/>
+      <c r="H129" s="21"/>
+    </row>
+    <row r="131" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B131" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="C131" s="23"/>
+      <c r="D131" s="23"/>
+      <c r="E131" s="23"/>
+      <c r="F131" s="23"/>
+      <c r="G131" s="23"/>
+      <c r="H131" s="23"/>
+    </row>
+    <row r="132" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B132" s="23"/>
+      <c r="C132" s="23"/>
+      <c r="D132" s="23"/>
+      <c r="E132" s="23"/>
+      <c r="F132" s="23"/>
+      <c r="G132" s="23"/>
+      <c r="H132" s="23"/>
+    </row>
+    <row r="133" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B133" s="23"/>
+      <c r="C133" s="23"/>
+      <c r="D133" s="23"/>
+      <c r="E133" s="23"/>
+      <c r="F133" s="23"/>
+      <c r="G133" s="23"/>
+      <c r="H133" s="23"/>
+    </row>
+    <row r="134" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B134" s="23"/>
+      <c r="C134" s="23"/>
+      <c r="D134" s="23"/>
+      <c r="E134" s="23"/>
+      <c r="F134" s="23"/>
+      <c r="G134" s="23"/>
+      <c r="H134" s="23"/>
+    </row>
+    <row r="135" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B135" s="23"/>
+      <c r="C135" s="23"/>
+      <c r="D135" s="23"/>
+      <c r="E135" s="23"/>
+      <c r="F135" s="23"/>
+      <c r="G135" s="23"/>
+      <c r="H135" s="23"/>
+    </row>
+    <row r="136" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B136" s="23"/>
+      <c r="C136" s="23"/>
+      <c r="D136" s="23"/>
+      <c r="E136" s="23"/>
+      <c r="F136" s="23"/>
+      <c r="G136" s="23"/>
+      <c r="H136" s="23"/>
     </row>
     <row r="138" spans="2:8" ht="15" customHeight="1">
       <c r="B138" s="13" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="C138" s="21"/>
       <c r="D138" s="21"/>
@@ -4728,135 +4464,68 @@
       <c r="G138" s="21"/>
       <c r="H138" s="21"/>
     </row>
-    <row r="140" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B140" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="C140" s="23"/>
-      <c r="D140" s="23"/>
-      <c r="E140" s="23"/>
-      <c r="F140" s="23"/>
-      <c r="G140" s="23"/>
-      <c r="H140" s="23"/>
-    </row>
-    <row r="141" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B141" s="23"/>
-      <c r="C141" s="23"/>
-      <c r="D141" s="23"/>
-      <c r="E141" s="23"/>
-      <c r="F141" s="23"/>
-      <c r="G141" s="23"/>
-      <c r="H141" s="23"/>
-    </row>
-    <row r="142" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B142" s="23"/>
-      <c r="C142" s="23"/>
-      <c r="D142" s="23"/>
-      <c r="E142" s="23"/>
-      <c r="F142" s="23"/>
-      <c r="G142" s="23"/>
-      <c r="H142" s="23"/>
-    </row>
-    <row r="143" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B143" s="23"/>
-      <c r="C143" s="23"/>
-      <c r="D143" s="23"/>
-      <c r="E143" s="23"/>
-      <c r="F143" s="23"/>
-      <c r="G143" s="23"/>
-      <c r="H143" s="23"/>
-    </row>
-    <row r="144" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B144" s="23"/>
-      <c r="C144" s="23"/>
-      <c r="D144" s="23"/>
-      <c r="E144" s="23"/>
-      <c r="F144" s="23"/>
-      <c r="G144" s="23"/>
-      <c r="H144" s="23"/>
-    </row>
-    <row r="145" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B145" s="23"/>
-      <c r="C145" s="23"/>
-      <c r="D145" s="23"/>
-      <c r="E145" s="23"/>
-      <c r="F145" s="23"/>
-      <c r="G145" s="23"/>
-      <c r="H145" s="23"/>
-    </row>
-    <row r="147" spans="2:8" ht="15" customHeight="1">
-      <c r="B147" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="C147" s="21"/>
-      <c r="D147" s="21"/>
-      <c r="E147" s="21"/>
-      <c r="F147" s="21"/>
-      <c r="G147" s="21"/>
-      <c r="H147" s="21"/>
-    </row>
-    <row r="148" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B148" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="C148" s="21"/>
-      <c r="D148" s="21"/>
-      <c r="E148" s="21"/>
-      <c r="F148" s="21"/>
-      <c r="G148" s="21"/>
-      <c r="H148" s="21"/>
-    </row>
-    <row r="149" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B149" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="C149" s="21"/>
-      <c r="D149" s="21"/>
-      <c r="E149" s="21"/>
-      <c r="F149" s="21"/>
-      <c r="G149" s="21"/>
-      <c r="H149" s="21"/>
-    </row>
-    <row r="150" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B150" s="24" t="s">
-        <v>227</v>
-      </c>
-      <c r="C150" s="21"/>
-      <c r="D150" s="21"/>
-      <c r="E150" s="21"/>
-      <c r="F150" s="21"/>
-      <c r="G150" s="21"/>
-      <c r="H150" s="21"/>
-    </row>
-    <row r="153" ht="15">
-      <c r="B153" s="21" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="168" ht="15">
-      <c r="B168" s="21" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="169" ht="15">
-      <c r="B169" s="21" t="s">
-        <v>230</v>
+    <row r="139" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B139" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="C139" s="21"/>
+      <c r="D139" s="21"/>
+      <c r="E139" s="21"/>
+      <c r="F139" s="21"/>
+      <c r="G139" s="21"/>
+      <c r="H139" s="21"/>
+    </row>
+    <row r="140" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B140" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="C140" s="21"/>
+      <c r="D140" s="21"/>
+      <c r="E140" s="21"/>
+      <c r="F140" s="21"/>
+      <c r="G140" s="21"/>
+      <c r="H140" s="21"/>
+    </row>
+    <row r="141" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B141" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="C141" s="21"/>
+      <c r="D141" s="21"/>
+      <c r="E141" s="21"/>
+      <c r="F141" s="21"/>
+      <c r="G141" s="21"/>
+      <c r="H141" s="21"/>
+    </row>
+    <row r="144" ht="15">
+      <c r="B144" s="21" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="159" ht="15">
+      <c r="B159" s="21" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="160" ht="15">
+      <c r="B160" s="21" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B149:H149"/>
-    <mergeCell ref="B150:H150"/>
-    <mergeCell ref="B136:H136"/>
+    <mergeCell ref="B140:H140"/>
+    <mergeCell ref="B141:H141"/>
+    <mergeCell ref="B127:H127"/>
+    <mergeCell ref="B129:H129"/>
+    <mergeCell ref="B131:H136"/>
     <mergeCell ref="B138:H138"/>
-    <mergeCell ref="B140:H145"/>
-    <mergeCell ref="B147:H147"/>
-    <mergeCell ref="B148:H148"/>
+    <mergeCell ref="B139:H139"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B131:I131"/>
-    <mergeCell ref="B135:I135"/>
+    <mergeCell ref="B122:I122"/>
+    <mergeCell ref="B126:I126"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
